--- a/utils/Tools/excel/20_task_任务.xlsx
+++ b/utils/Tools/excel/20_task_任务.xlsx
@@ -107,7 +107,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="28">
   <si>
     <t>任务id</t>
   </si>
@@ -191,12 +191,6 @@
   </si>
   <si>
     <t>cs</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -1536,28 +1530,28 @@
         <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>27</v>
